--- a/시흥캠퍼스_식당카페_조사표_통합.xlsx
+++ b/시흥캠퍼스_식당카페_조사표_통합.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="대분류목록">카테고리!$D$2:$D$3</definedName>
-    <definedName name="식당">카테고리!$A$2:$A$13</definedName>
+    <definedName name="식당">카테고리!$A$2:$A$14</definedName>
     <definedName name="카페">카테고리!$B$2:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'매장·메뉴 입력'!$A$1:$N$610</definedName>
   </definedNames>
@@ -35978,7 +35978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -36107,6 +36107,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="141" t="inlineStr">
+        <is>
+          <t>도시락</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/시흥캠퍼스_식당카페_조사표_통합.xlsx
+++ b/시흥캠퍼스_식당카페_조사표_통합.xlsx
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J27" s="113" t="inlineStr">
         <is>
-          <t>17~32(알뜰배달)</t>
+          <t>17~32</t>
         </is>
       </c>
       <c r="K27" s="6" t="n">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="J28" s="113" t="inlineStr">
         <is>
-          <t>17~32(알뜰배달)</t>
+          <t>17~32</t>
         </is>
       </c>
       <c r="K28" s="6" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="J29" s="113" t="inlineStr">
         <is>
-          <t>17~32(알뜰배달)</t>
+          <t>17~32</t>
         </is>
       </c>
       <c r="K29" s="6" t="n">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="J30" s="113" t="inlineStr">
         <is>
-          <t>17~32(알뜰배달)</t>
+          <t>17~32</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="J31" s="113" t="inlineStr">
         <is>
-          <t>17~32(알뜰배달)</t>
+          <t>17~32</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J67" s="113" t="inlineStr">
         <is>
-          <t>23~38(알뜰배달)</t>
+          <t>23~38</t>
         </is>
       </c>
       <c r="K67" s="6" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="J68" s="113" t="inlineStr">
         <is>
-          <t>23~38(알뜰배달)</t>
+          <t>23~38</t>
         </is>
       </c>
       <c r="K68" s="6" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="J69" s="113" t="inlineStr">
         <is>
-          <t>23~38(알뜰배달)</t>
+          <t>23~38</t>
         </is>
       </c>
       <c r="K69" s="6" t="n">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J70" s="113" t="inlineStr">
         <is>
-          <t>23~38(알뜰배달)</t>
+          <t>23~38</t>
         </is>
       </c>
       <c r="K70" s="6" t="n">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="J71" s="113" t="inlineStr">
         <is>
-          <t>23~38(알뜰배달)</t>
+          <t>23~38</t>
         </is>
       </c>
       <c r="K71" s="6" t="n">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄리스 배곧 1차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄팰리스 배곧1차)</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄리스 배곧 1차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄팰리스 배곧1차)</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄리스 배곧 1차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄팰리스 배곧1차)</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄리스 배곧 1차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄팰리스 배곧1차)</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄리스 배곧 1차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-24 103-104호(배곧동, 다인로얄팰리스 배곧1차)</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 (정 왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 (정왕동)</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 (정 왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 (정왕동)</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 (정 왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 (정왕동)</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 (정 왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 (정왕동)</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 (정 왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 (정왕동)</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 옐로우)</t>
+          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브뉴프랑 센트럴 옐로우)</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 옐로우)</t>
+          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브뉴프랑 센트럴 옐로우)</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -18083,7 +18083,7 @@
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 옐로우)</t>
+          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브뉴프랑 센트럴 옐로우)</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 옐로우)</t>
+          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브뉴프랑 센트럴 옐로우)</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -18207,7 +18207,7 @@
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 옐로우)</t>
+          <t>경기도 시흥시 서울대학로278번길 34 2층 203,204호(배곧동, 시흥배곧 아브뉴프랑 센트럴 옐로우)</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 군서마을로 62 1층일부 호(정왕동)</t>
+          <t>경기도 시흥시 군서마을로 62 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 군서마을로 62 1층일부 호(정왕동)</t>
+          <t>경기도 시흥시 군서마을로 62 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 군서마을로 62 1층일부 호(정왕동)</t>
+          <t>경기도 시흥시 군서마을로 62 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 군서마을로 62 1층일부 호(정왕동)</t>
+          <t>경기도 시흥시 군서마을로 62 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 군서마을로 62 1층일부 호(정왕동)</t>
+          <t>경기도 시흥시 군서마을로 62 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서촌상가4길 10 1층 106 호(정왕동,한솔빌딩)</t>
+          <t>경기도 시흥시 서촌상가4길 10 1층 106호(정왕동, 한솔빌딩)</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="E315" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서촌상가4길 10 1층 106 호(정왕동,한솔빌딩)</t>
+          <t>경기도 시흥시 서촌상가4길 10 1층 106호(정왕동, 한솔빌딩)</t>
         </is>
       </c>
       <c r="F315" s="3" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서촌상가4길 10 1층 106 호(정왕동,한솔빌딩)</t>
+          <t>경기도 시흥시 서촌상가4길 10 1층 106호(정왕동, 한솔빌딩)</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="E317" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서촌상가4길 10 1층 106 호(정왕동,한솔빌딩)</t>
+          <t>경기도 시흥시 서촌상가4길 10 1층 106호(정왕동, 한솔빌딩)</t>
         </is>
       </c>
       <c r="F317" s="3" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서촌상가4길 10 1층 106 호(정왕동,한솔빌딩)</t>
+          <t>경기도 시흥시 서촌상가4길 10 1층 106호(정왕동, 한솔빌딩)</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="E319" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄 팰리스 배곧2차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄팰리스 배곧2차)</t>
         </is>
       </c>
       <c r="F319" s="3" t="inlineStr">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄 팰리스 배곧2차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄팰리스 배곧2차)</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="E321" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄 팰리스 배곧2차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄팰리스 배곧2차)</t>
         </is>
       </c>
       <c r="F321" s="3" t="inlineStr">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄 팰리스 배곧2차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄팰리스 배곧2차)</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr">
@@ -21927,7 +21927,7 @@
       </c>
       <c r="E323" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄 팰리스 배곧2차)</t>
+          <t>경기도 시흥시 서울대학로278번길 25-32 1층 102호(배곧동, 다인로얄팰리스 배곧2차)</t>
         </is>
       </c>
       <c r="F323" s="3" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="E333" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 오동마을로 9 1층 일부 호(정왕동)</t>
+          <t>경기도 시흥시 오동마을로 9 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F333" s="3" t="inlineStr">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 오동마을로 9 1층 일부 호(정왕동)</t>
+          <t>경기도 시흥시 오동마을로 9 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr">
@@ -22671,7 +22671,7 @@
       </c>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 오동마을로 9 1층 일부 호(정왕동)</t>
+          <t>경기도 시흥시 오동마을로 9 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F335" s="3" t="inlineStr">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 오동마을로 9 1층 일부 호(정왕동)</t>
+          <t>경기도 시흥시 오동마을로 9 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 오동마을로 9 1층 일부 호(정왕동)</t>
+          <t>경기도 시흥시 오동마을로 9 1층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F337" s="3" t="inlineStr">
@@ -22857,7 +22857,7 @@
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 다솜마을2길 23 103 호(정왕동)</t>
+          <t>경기도 시흥시 다솜마을2길 23 103호(정왕동)</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr">
@@ -22919,7 +22919,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 다솜마을2길 23 103 호(정왕동)</t>
+          <t>경기도 시흥시 다솜마을2길 23 103호(정왕동)</t>
         </is>
       </c>
       <c r="F339" s="3" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 다솜마을2길 23 103 호(정왕동)</t>
+          <t>경기도 시흥시 다솜마을2길 23 103호(정왕동)</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 다솜마을2길 23 103 호(정왕동)</t>
+          <t>경기도 시흥시 다솜마을2길 23 103호(정왕동)</t>
         </is>
       </c>
       <c r="F341" s="3" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 다솜마을2길 23 103 호(정왕동)</t>
+          <t>경기도 시흥시 다솜마을2길 23 103호(정왕동)</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr">
@@ -23167,7 +23167,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2311-5 1층 일 부(101)호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2311-5 1층 일부(101)호(정왕동)</t>
         </is>
       </c>
       <c r="F343" s="3" t="inlineStr">
@@ -23229,7 +23229,7 @@
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2311-5 1층 일 부(101)호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2311-5 1층 일부(101)호(정왕동)</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2311-5 1층 일 부(101)호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2311-5 1층 일부(101)호(정왕동)</t>
         </is>
       </c>
       <c r="F345" s="3" t="inlineStr">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2311-5 1층 일 부(101)호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2311-5 1층 일부(101)호(정왕동)</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr">
@@ -23415,7 +23415,7 @@
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2311-5 1층 일 부(101)호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2311-5 1층 일부(101)호(정왕동)</t>
         </is>
       </c>
       <c r="F347" s="3" t="inlineStr">
@@ -24035,7 +24035,7 @@
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라 자)</t>
+          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라자)</t>
         </is>
       </c>
       <c r="F357" s="3" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라 자)</t>
+          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라자)</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라 자)</t>
+          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라자)</t>
         </is>
       </c>
       <c r="F359" s="3" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라 자)</t>
+          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라자)</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라 자)</t>
+          <t>경기도 시흥시 중심상가2길 4-3, 1층 104,105호, 106호(정왕동, 완도프라자)</t>
         </is>
       </c>
       <c r="F361" s="3" t="inlineStr">
@@ -25167,11 +25167,11 @@
       </c>
       <c r="M376" s="3" t="inlineStr">
         <is>
-          <t>밥 포함)</t>
+          <t>[주문폭주] 셀프마라탕 + 볶음밥세트</t>
         </is>
       </c>
       <c r="N376" s="6" t="n">
-        <v>18000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 그린)</t>
+          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브뉴프랑 센트럴 그린)</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="E393" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 그린)</t>
+          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브뉴프랑 센트럴 그린)</t>
         </is>
       </c>
       <c r="F393" s="3" t="inlineStr">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 그린)</t>
+          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브뉴프랑 센트럴 그린)</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="E395" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 그린)</t>
+          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브뉴프랑 센트럴 그린)</t>
         </is>
       </c>
       <c r="F395" s="3" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브 뉴프랑 센트럴 그린)</t>
+          <t>경기도 시흥시 서울대학로264번길 35 1층 125호(배곧동, 시흥배곧 아브뉴프랑 센트럴 그린)</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr">
@@ -27365,7 +27365,7 @@
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 2 층 일부호(정왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 2층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr">
@@ -27427,7 +27427,7 @@
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 2 층 일부호(정왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 2층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F413" s="3" t="inlineStr">
@@ -27489,7 +27489,7 @@
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 2 층 일부호(정왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 2층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr">
@@ -27551,7 +27551,7 @@
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 2 층 일부호(정왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 2층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F415" s="3" t="inlineStr">
@@ -27613,7 +27613,7 @@
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로14번길 5-16 2 층 일부호(정왕동)</t>
+          <t>경기도 시흥시 함송로14번길 5-16 2층 일부호(정왕동)</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr">
@@ -28295,7 +28295,7 @@
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로13번길 6-13 1 층 101,102,103호(정왕동, 탑빌딩)</t>
+          <t>경기도 시흥시 함송로13번길 6-13 1층 101,102,103호(정왕동, 탑빌딩)</t>
         </is>
       </c>
       <c r="F427" s="3" t="inlineStr">
@@ -28357,7 +28357,7 @@
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로13번길 6-13 1 층 101,102,103호(정왕동, 탑빌딩)</t>
+          <t>경기도 시흥시 함송로13번길 6-13 1층 101,102,103호(정왕동, 탑빌딩)</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr">
@@ -28419,7 +28419,7 @@
       </c>
       <c r="E429" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로13번길 6-13 1 층 101,102,103호(정왕동, 탑빌딩)</t>
+          <t>경기도 시흥시 함송로13번길 6-13 1층 101,102,103호(정왕동, 탑빌딩)</t>
         </is>
       </c>
       <c r="F429" s="3" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로13번길 6-13 1 층 101,102,103호(정왕동, 탑빌딩)</t>
+          <t>경기도 시흥시 함송로13번길 6-13 1층 101,102,103호(정왕동, 탑빌딩)</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr">
@@ -28543,7 +28543,7 @@
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 함송로13번길 6-13 1 층 101,102,103호(정왕동, 탑빌딩)</t>
+          <t>경기도 시흥시 함송로13번길 6-13 1층 101,102,103호(정왕동, 탑빌딩)</t>
         </is>
       </c>
       <c r="F431" s="3" t="inlineStr">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 180 ,모아프 라자 1층 108,109호(정왕동)</t>
+          <t>경기도 시흥시 중심상가로 180, 모아프라자 1층 108,109호(정왕동)</t>
         </is>
       </c>
       <c r="F449" s="3" t="inlineStr">
@@ -29721,7 +29721,7 @@
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 180 ,모아프 라자 1층 108,109호(정왕동)</t>
+          <t>경기도 시흥시 중심상가로 180, 모아프라자 1층 108,109호(정왕동)</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr">
@@ -29783,7 +29783,7 @@
       </c>
       <c r="E451" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 180 ,모아프 라자 1층 108,109호(정왕동)</t>
+          <t>경기도 시흥시 중심상가로 180, 모아프라자 1층 108,109호(정왕동)</t>
         </is>
       </c>
       <c r="F451" s="3" t="inlineStr">
@@ -29845,7 +29845,7 @@
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 180 ,모아프 라자 1층 108,109호(정왕동)</t>
+          <t>경기도 시흥시 중심상가로 180, 모아프라자 1층 108,109호(정왕동)</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr">
@@ -29907,7 +29907,7 @@
       </c>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 180 ,모아프 라자 1층 108,109호(정왕동)</t>
+          <t>경기도 시흥시 중심상가로 180, 모아프라자 1층 108,109호(정왕동)</t>
         </is>
       </c>
       <c r="F453" s="3" t="inlineStr">
@@ -30217,7 +30217,7 @@
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이 - 164호(배곧동, 시 흥배곧 C1 호반 써밋플레이스)</t>
+          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이-164호(배곧동, 시흥배곧 C1 호반 써밋플레이스)</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr">
@@ -30279,7 +30279,7 @@
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이 - 164호(배곧동, 시 흥배곧 C1 호반 써밋플레이스)</t>
+          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이-164호(배곧동, 시흥배곧 C1 호반 써밋플레이스)</t>
         </is>
       </c>
       <c r="F459" s="3" t="inlineStr">
@@ -30341,7 +30341,7 @@
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이 - 164호(배곧동, 시 흥배곧 C1 호반 써밋플레이스)</t>
+          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이-164호(배곧동, 시흥배곧 C1 호반 써밋플레이스)</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr">
@@ -30403,7 +30403,7 @@
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이 - 164호(배곧동, 시 흥배곧 C1 호반 써밋플레이스)</t>
+          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이-164호(배곧동, 시흥배곧 C1 호반 써밋플레이스)</t>
         </is>
       </c>
       <c r="F461" s="3" t="inlineStr">
@@ -30465,7 +30465,7 @@
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이 - 164호(배곧동, 시 흥배곧 C1 호반 써밋플레이스)</t>
+          <t>경기도 시흥시 서울대학로278번길 19-13 107동 에이-164호(배곧동, 시흥배곧 C1 호반 써밋플레이스)</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프 랑 센트럴 레드)</t>
+          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프랑 센트럴 레드)</t>
         </is>
       </c>
       <c r="F463" s="3" t="inlineStr">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프 랑 센트럴 레드)</t>
+          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프랑 센트럴 레드)</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr">
@@ -30651,7 +30651,7 @@
       </c>
       <c r="E465" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프 랑 센트럴 레드)</t>
+          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프랑 센트럴 레드)</t>
         </is>
       </c>
       <c r="F465" s="3" t="inlineStr">
@@ -30713,7 +30713,7 @@
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프 랑 센트럴 레드)</t>
+          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프랑 센트럴 레드)</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr">
@@ -30775,7 +30775,7 @@
       </c>
       <c r="E467" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프 랑 센트럴 레드)</t>
+          <t>경기도 시흥시 서울대학로278번길 8 1층 A-144호(배곧동, 시흥배곧 아브뉴프랑 센트럴 레드)</t>
         </is>
       </c>
       <c r="F467" s="3" t="inlineStr">
@@ -30837,12 +30837,12 @@
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 187 1층 103 호(정왕동, 진명프라자)</t>
+          <t>경기도 시흥시 중심상가로 187 1층 103호(정왕동, 진명프라자)</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:0( 목요일 - 오전 11:00 ~밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
+          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:00 목요일 - 오전 11:00 ~ 밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
@@ -30899,12 +30899,12 @@
       </c>
       <c r="E469" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 187 1층 103 호(정왕동, 진명프라자)</t>
+          <t>경기도 시흥시 중심상가로 187 1층 103호(정왕동, 진명프라자)</t>
         </is>
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
-          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:0( 목요일 - 오전 11:00 ~밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
+          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:00 목요일 - 오전 11:00 ~ 밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
         </is>
       </c>
       <c r="G469" s="3" t="inlineStr">
@@ -30961,12 +30961,12 @@
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 187 1층 103 호(정왕동, 진명프라자)</t>
+          <t>경기도 시흥시 중심상가로 187 1층 103호(정왕동, 진명프라자)</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:0( 목요일 - 오전 11:00 ~밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
+          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:00 목요일 - 오전 11:00 ~ 밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -31023,12 +31023,12 @@
       </c>
       <c r="E471" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 187 1층 103 호(정왕동, 진명프라자)</t>
+          <t>경기도 시흥시 중심상가로 187 1층 103호(정왕동, 진명프라자)</t>
         </is>
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:0( 목요일 - 오전 11:00 ~밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
+          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:00 목요일 - 오전 11:00 ~ 밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -31085,12 +31085,12 @@
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 187 1층 103 호(정왕동, 진명프라자)</t>
+          <t>경기도 시흥시 중심상가로 187 1층 103호(정왕동, 진명프라자)</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:0( 목요일 - 오전 11:00 ~밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
+          <t>화요일 - 오전 11:00 ~ 밤 12:00 수요일 - 오전 11:00 ~ 밤 12:00 목요일 - 오전 11:00 ~ 밤 12:00 금요일 - 오전 11:00 ~ 익일 새벽 2:00 토요일 - 오전 11:00 ~ 익일 새벽 2:00 일요일 - 오전 11:00 ~ 오후 10:00 월요일 - 오전 11:00 ~ 밤 12:00</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2519-1 배곧 유호 N-CITY 1차 1층 136호 (정왕동)</t>
+          <t>경기도 시흥시 정왕동 2519-1 배곧유호 N-CITY 1차 1층 136호 (정왕동)</t>
         </is>
       </c>
       <c r="F473" s="3" t="inlineStr">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2519-1 배곧 유호 N-CITY 1차 1층 136호 (정왕동)</t>
+          <t>경기도 시흥시 정왕동 2519-1 배곧유호 N-CITY 1차 1층 136호 (정왕동)</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr">
@@ -31271,7 +31271,7 @@
       </c>
       <c r="E475" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2519-1 배곧 유호 N-CITY 1차 1층 136호 (정왕동)</t>
+          <t>경기도 시흥시 정왕동 2519-1 배곧유호 N-CITY 1차 1층 136호 (정왕동)</t>
         </is>
       </c>
       <c r="F475" s="3" t="inlineStr">
@@ -31333,7 +31333,7 @@
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2519-1 배곧 유호 N-CITY 1차 1층 136호 (정왕동)</t>
+          <t>경기도 시흥시 정왕동 2519-1 배곧유호 N-CITY 1차 1층 136호 (정왕동)</t>
         </is>
       </c>
       <c r="F476" s="3" t="inlineStr">
@@ -31395,7 +31395,7 @@
       </c>
       <c r="E477" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2519-1 배곧 유호 N-CITY 1차 1층 136호 (정왕동)</t>
+          <t>경기도 시흥시 정왕동 2519-1 배곧유호 N-CITY 1차 1층 136호 (정왕동)</t>
         </is>
       </c>
       <c r="F477" s="3" t="inlineStr">
@@ -31457,7 +31457,7 @@
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧아브뉴프 랑 센트럴 블루)</t>
+          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧 아브뉴프랑 센트럴 블루)</t>
         </is>
       </c>
       <c r="F478" s="3" t="inlineStr">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧아브뉴프 랑 센트럴 블루)</t>
+          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧 아브뉴프랑 센트럴 블루)</t>
         </is>
       </c>
       <c r="F479" s="3" t="inlineStr">
@@ -31581,7 +31581,7 @@
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧아브뉴프 랑 센트럴 블루)</t>
+          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧 아브뉴프랑 센트럴 블루)</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr">
@@ -31643,7 +31643,7 @@
       </c>
       <c r="E481" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧아브뉴프 랑 센트럴 블루)</t>
+          <t>경기도 시흥시 서울대학로264번길 25 103,104호(배곧동, 시흥배곧 아브뉴프랑 센트럴 블루)</t>
         </is>
       </c>
       <c r="F481" s="3" t="inlineStr">
@@ -31705,7 +31705,7 @@
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2522 시흥배곧 아 브뉴프랑센트럴 레드 1층 B-136,B-137 호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2522 시흥배곧 아브뉴프랑 센트럴 레드 1층 B-136,B-137호(정왕동)</t>
         </is>
       </c>
       <c r="F482" s="3" t="inlineStr">
@@ -31767,7 +31767,7 @@
       </c>
       <c r="E483" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2522 시흥배곧 아 브뉴프랑센트럴 레드 1층 B-136,B-137 호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2522 시흥배곧 아브뉴프랑 센트럴 레드 1층 B-136,B-137호(정왕동)</t>
         </is>
       </c>
       <c r="F483" s="3" t="inlineStr">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2522 시흥배곧 아 브뉴프랑센트럴 레드 1층 B-136,B-137 호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2522 시흥배곧 아브뉴프랑 센트럴 레드 1층 B-136,B-137호(정왕동)</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr">
@@ -31891,7 +31891,7 @@
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2522 시흥배곧 아 브뉴프랑센트럴 레드 1층 B-136,B-137 호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2522 시흥배곧 아브뉴프랑 센트럴 레드 1층 B-136,B-137호(정왕동)</t>
         </is>
       </c>
       <c r="F485" s="3" t="inlineStr">
@@ -31953,7 +31953,7 @@
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 정왕동 2522 시흥배곧 아 브뉴프랑센트럴 레드 1층 B-136,B-137 호(정왕동)</t>
+          <t>경기도 시흥시 정왕동 2522 시흥배곧 아브뉴프랑 센트럴 레드 1층 B-136,B-137호(정왕동)</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr">
@@ -32015,7 +32015,7 @@
       </c>
       <c r="E487" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 178 한라프라 자 104호, 105호 (정왕동)</t>
+          <t>경기도 시흥시 중심상가로 178 한라프라자 104호, 105호 (정왕동)</t>
         </is>
       </c>
       <c r="F487" s="3" t="inlineStr">
@@ -32077,7 +32077,7 @@
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 178 한라프라 자 104호, 105호 (정왕동)</t>
+          <t>경기도 시흥시 중심상가로 178 한라프라자 104호, 105호 (정왕동)</t>
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr">
@@ -32139,7 +32139,7 @@
       </c>
       <c r="E489" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 178 한라프라 자 104호, 105호 (정왕동)</t>
+          <t>경기도 시흥시 중심상가로 178 한라프라자 104호, 105호 (정왕동)</t>
         </is>
       </c>
       <c r="F489" s="3" t="inlineStr">
@@ -32201,7 +32201,7 @@
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 178 한라프라 자 104호, 105호 (정왕동)</t>
+          <t>경기도 시흥시 중심상가로 178 한라프라자 104호, 105호 (정왕동)</t>
         </is>
       </c>
       <c r="F490" s="3" t="inlineStr">
@@ -32263,7 +32263,7 @@
       </c>
       <c r="E491" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 중심상가로 178 한라프라 자 104호, 105호 (정왕동)</t>
+          <t>경기도 시흥시 중심상가로 178 한라프라자 104호, 105호 (정왕동)</t>
         </is>
       </c>
       <c r="F491" s="3" t="inlineStr">
@@ -32325,7 +32325,7 @@
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동,시흥배곧 아 브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr">
@@ -32387,7 +32387,7 @@
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동,시흥배곧 아 브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F493" s="3" t="inlineStr">
@@ -32449,7 +32449,7 @@
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동,시흥배곧 아 브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F494" s="3" t="inlineStr">
@@ -32511,7 +32511,7 @@
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동,시흥배곧 아 브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F495" s="3" t="inlineStr">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동,시흥배곧 아 브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 B-138호,B-139호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F496" s="3" t="inlineStr">
@@ -33255,7 +33255,7 @@
       </c>
       <c r="E507" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중 앙프라자)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중앙프라자)</t>
         </is>
       </c>
       <c r="F507" s="3" t="inlineStr">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중 앙프라자)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중앙프라자)</t>
         </is>
       </c>
       <c r="F508" s="3" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="E509" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중 앙프라자)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중앙프라자)</t>
         </is>
       </c>
       <c r="F509" s="3" t="inlineStr">
@@ -33441,7 +33441,7 @@
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중 앙프라자)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중앙프라자)</t>
         </is>
       </c>
       <c r="F510" s="3" t="inlineStr">
@@ -33503,7 +33503,7 @@
       </c>
       <c r="E511" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중 앙프라자)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 7층 712호,713호(배곧동, 배곧중앙프라자)</t>
         </is>
       </c>
       <c r="F511" s="3" t="inlineStr">
@@ -33565,7 +33565,7 @@
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정 왕동)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정왕동)</t>
         </is>
       </c>
       <c r="F512" s="3" t="inlineStr">
@@ -33627,7 +33627,7 @@
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정 왕동)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정왕동)</t>
         </is>
       </c>
       <c r="F513" s="3" t="inlineStr">
@@ -33689,7 +33689,7 @@
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정 왕동)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정왕동)</t>
         </is>
       </c>
       <c r="F514" s="3" t="inlineStr">
@@ -33751,7 +33751,7 @@
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정 왕동)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정왕동)</t>
         </is>
       </c>
       <c r="F515" s="3" t="inlineStr">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정 왕동)</t>
+          <t>경기도 시흥시 서울대학로264번길 26-32 배곧중앙프라자 142 일부호 (정왕동)</t>
         </is>
       </c>
       <c r="F516" s="3" t="inlineStr">
@@ -34185,7 +34185,7 @@
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 A 동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 A동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F522" s="3" t="inlineStr">
@@ -34247,7 +34247,7 @@
       </c>
       <c r="E523" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 A 동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 A동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F523" s="3" t="inlineStr">
@@ -34309,7 +34309,7 @@
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 A 동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 A동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F524" s="3" t="inlineStr">
@@ -34371,7 +34371,7 @@
       </c>
       <c r="E525" s="3" t="inlineStr">
         <is>
-          <t>경기도 시흥시 서울대학로264번길 7 A 동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
+          <t>경기도 시흥시 서울대학로264번길 7 A동 314호(배곧동, 시흥배곧 아브뉴프랑 센트럴 퍼플)</t>
         </is>
       </c>
       <c r="F525" s="3" t="inlineStr">
@@ -35978,7 +35978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -36114,11 +36114,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
